--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.60705905410793</v>
+        <v>10.33614709629254</v>
       </c>
       <c r="D2" t="n">
-        <v>80.90696852031979</v>
+        <v>13.14738238455197</v>
       </c>
       <c r="E2" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F2" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.03618896656821</v>
+        <v>6.668380707067334</v>
       </c>
       <c r="D3" t="n">
-        <v>52.46739734919741</v>
+        <v>8.525952069244578</v>
       </c>
       <c r="E3" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F3" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.80497530281752</v>
+        <v>8.093308486707848</v>
       </c>
       <c r="D4" t="n">
-        <v>71.35904626834294</v>
+        <v>11.59584501860573</v>
       </c>
       <c r="E4" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F4" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.62924877018251</v>
+        <v>3.677252925154658</v>
       </c>
       <c r="D5" t="n">
-        <v>32.79815319826819</v>
+        <v>5.329699894718581</v>
       </c>
       <c r="E5" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F5" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.51997507482711</v>
+        <v>5.609495949659405</v>
       </c>
       <c r="D6" t="n">
-        <v>13.72016512344486</v>
+        <v>2.229526832559791</v>
       </c>
       <c r="E6" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F6" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.33015016715721</v>
+        <v>5.091149402163047</v>
       </c>
       <c r="D7" t="n">
-        <v>13.66910289827714</v>
+        <v>2.221229220970035</v>
       </c>
       <c r="E7" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F7" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.05163403968101</v>
+        <v>3.583390531448165</v>
       </c>
       <c r="D8" t="n">
-        <v>10.55393385822255</v>
+        <v>1.715014251961164</v>
       </c>
       <c r="E8" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F8" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.53037231908192</v>
+        <v>6.423685501850812</v>
       </c>
       <c r="D9" t="n">
-        <v>26.65771453593921</v>
+        <v>4.331878612090122</v>
       </c>
       <c r="E9" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F9" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>10.50430971847934</v>
+        <v>1.706950329252893</v>
       </c>
       <c r="D10" t="n">
-        <v>18.97345422176999</v>
+        <v>3.083186311037624</v>
       </c>
       <c r="E10" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F10" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>8.134818253097748</v>
+        <v>1.321907966128384</v>
       </c>
       <c r="D11" t="n">
-        <v>51.75423603988858</v>
+        <v>8.410063356481896</v>
       </c>
       <c r="E11" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F11" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>7.41297006250648</v>
+        <v>1.204607635157303</v>
       </c>
       <c r="D12" t="n">
-        <v>24.95985010915348</v>
+        <v>4.05597564273744</v>
       </c>
       <c r="E12" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F12" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.70509936587179</v>
+        <v>4.014578646954166</v>
       </c>
       <c r="D13" t="n">
-        <v>55.80996608306369</v>
+        <v>9.069119488497849</v>
       </c>
       <c r="E13" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F13" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.08114590350897</v>
+        <v>3.425686209320208</v>
       </c>
       <c r="D14" t="n">
-        <v>20.60282092958736</v>
+        <v>3.347958401057945</v>
       </c>
       <c r="E14" t="n">
-        <v>16.01823012166811</v>
+        <v>2.602962394771068</v>
       </c>
       <c r="F14" t="n">
-        <v>22.47163898563601</v>
+        <v>3.651641335165852</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
